--- a/astro-site/public/dl/kit-tareas-dark-kitchen/05-tareas-semanales-mensuales.xlsx
+++ b/astro-site/public/dl/kit-tareas-dark-kitchen/05-tareas-semanales-mensuales.xlsx
@@ -222,7 +222,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -310,6 +310,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -788,6 +794,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21" ht="18" customHeight="1">
       <c r="B21" s="23" t="inlineStr">
         <is>
@@ -795,6 +802,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23" ht="32" customHeight="1">
       <c r="B23" s="24" t="inlineStr">
         <is>
@@ -809,6 +817,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="18" customHeight="1">
       <c r="B26" s="23" t="inlineStr">
         <is>
@@ -816,6 +825,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28" ht="16" customHeight="1">
       <c r="B28" s="24" t="inlineStr">
         <is>
@@ -851,6 +861,7 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="23" t="inlineStr">
         <is>
@@ -858,6 +869,7 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
     <row r="36" ht="35" customHeight="1">
       <c r="B36" s="23" t="inlineStr">
         <is>
@@ -872,6 +884,7 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="23" t="inlineStr">
         <is>
@@ -977,10 +990,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="D6" s="9" t="n">
+        <v>5</v>
       </c>
       <c r="E6" s="10">
         <f>IF(B6="","",IF(B6&lt;D6,"⚠️ PEDIR","OK"))</f>
@@ -1000,10 +1011,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="D7" s="13" t="n">
+        <v>3</v>
       </c>
       <c r="E7" s="14">
         <f>IF(B7="","",IF(B7&lt;D7,"⚠️ PEDIR","OK"))</f>
@@ -1023,10 +1032,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="D8" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="E8" s="10">
         <f>IF(B8="","",IF(B8&lt;D8,"⚠️ PEDIR","OK"))</f>
@@ -1046,10 +1053,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D9" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="E9" s="14">
         <f>IF(B9="","",IF(B9&lt;D9,"⚠️ PEDIR","OK"))</f>
@@ -1076,10 +1081,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="D11" s="13" t="n">
+        <v>5</v>
       </c>
       <c r="E11" s="14">
         <f>IF(B11="","",IF(B11&lt;D11,"⚠️ PEDIR","OK"))</f>
@@ -1099,10 +1102,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="D12" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="E12" s="10">
         <f>IF(B12="","",IF(B12&lt;D12,"⚠️ PEDIR","OK"))</f>
@@ -1122,10 +1123,8 @@
           <t>uds</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="D13" s="13" t="n">
+        <v>30</v>
       </c>
       <c r="E13" s="14">
         <f>IF(B13="","",IF(B13&lt;D13,"⚠️ PEDIR","OK"))</f>
@@ -1145,10 +1144,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D14" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="E14" s="10">
         <f>IF(B14="","",IF(B14&lt;D14,"⚠️ PEDIR","OK"))</f>
@@ -1175,10 +1172,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="D16" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="E16" s="10">
         <f>IF(B16="","",IF(B16&lt;D16,"⚠️ PEDIR","OK"))</f>
@@ -1198,10 +1193,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="D17" s="13" t="n">
+        <v>2</v>
       </c>
       <c r="E17" s="14">
         <f>IF(B17="","",IF(B17&lt;D17,"⚠️ PEDIR","OK"))</f>
@@ -1221,10 +1214,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="D18" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="E18" s="10">
         <f>IF(B18="","",IF(B18&lt;D18,"⚠️ PEDIR","OK"))</f>
@@ -1244,10 +1235,8 @@
           <t>uds</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="D19" s="13" t="n">
+        <v>8</v>
       </c>
       <c r="E19" s="14">
         <f>IF(B19="","",IF(B19&lt;D19,"⚠️ PEDIR","OK"))</f>
@@ -1267,10 +1256,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D20" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="E20" s="10">
         <f>IF(B20="","",IF(B20&lt;D20,"⚠️ PEDIR","OK"))</f>
@@ -1290,10 +1277,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="D21" s="13" t="n">
+        <v>0.5</v>
       </c>
       <c r="E21" s="14">
         <f>IF(B21="","",IF(B21&lt;D21,"⚠️ PEDIR","OK"))</f>
@@ -1320,10 +1305,8 @@
           <t>L</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D23" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="E23" s="14">
         <f>IF(B23="","",IF(B23&lt;D23,"⚠️ PEDIR","OK"))</f>
@@ -1343,10 +1326,8 @@
           <t>L</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="D24" s="9" t="n">
+        <v>0.5</v>
       </c>
       <c r="E24" s="10">
         <f>IF(B24="","",IF(B24&lt;D24,"⚠️ PEDIR","OK"))</f>
@@ -1366,10 +1347,8 @@
           <t>L</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="D25" s="13" t="n">
+        <v>0.5</v>
       </c>
       <c r="E25" s="14">
         <f>IF(B25="","",IF(B25&lt;D25,"⚠️ PEDIR","OK"))</f>
@@ -1389,10 +1368,8 @@
           <t>L</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D26" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="E26" s="10">
         <f>IF(B26="","",IF(B26&lt;D26,"⚠️ PEDIR","OK"))</f>
@@ -1412,10 +1389,8 @@
           <t>L</t>
         </is>
       </c>
-      <c r="D27" s="13" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="D27" s="13" t="n">
+        <v>0.5</v>
       </c>
       <c r="E27" s="14">
         <f>IF(B27="","",IF(B27&lt;D27,"⚠️ PEDIR","OK"))</f>
@@ -1435,10 +1410,8 @@
           <t>L</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="D28" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="E28" s="10">
         <f>IF(B28="","",IF(B28&lt;D28,"⚠️ PEDIR","OK"))</f>
@@ -1465,10 +1438,8 @@
           <t>uds</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="D30" s="9" t="n">
+        <v>50</v>
       </c>
       <c r="E30" s="10">
         <f>IF(B30="","",IF(B30&lt;D30,"⚠️ PEDIR","OK"))</f>
@@ -1488,10 +1459,8 @@
           <t>uds</t>
         </is>
       </c>
-      <c r="D31" s="13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="D31" s="13" t="n">
+        <v>50</v>
       </c>
       <c r="E31" s="14">
         <f>IF(B31="","",IF(B31&lt;D31,"⚠️ PEDIR","OK"))</f>
@@ -1511,10 +1480,8 @@
           <t>uds</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="D32" s="9" t="n">
+        <v>50</v>
       </c>
       <c r="E32" s="10">
         <f>IF(B32="","",IF(B32&lt;D32,"⚠️ PEDIR","OK"))</f>
@@ -1534,10 +1501,8 @@
           <t>uds</t>
         </is>
       </c>
-      <c r="D33" s="13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="D33" s="13" t="n">
+        <v>50</v>
       </c>
       <c r="E33" s="14">
         <f>IF(B33="","",IF(B33&lt;D33,"⚠️ PEDIR","OK"))</f>
@@ -1564,10 +1529,8 @@
           <t>uds</t>
         </is>
       </c>
-      <c r="D35" s="13" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+      <c r="D35" s="13" t="n">
+        <v>40</v>
       </c>
       <c r="E35" s="14">
         <f>IF(B35="","",IF(B35&lt;D35,"⚠️ PEDIR","OK"))</f>
@@ -1587,10 +1550,8 @@
           <t>uds</t>
         </is>
       </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+      <c r="D36" s="9" t="n">
+        <v>40</v>
       </c>
       <c r="E36" s="10">
         <f>IF(B36="","",IF(B36&lt;D36,"⚠️ PEDIR","OK"))</f>
@@ -1610,10 +1571,8 @@
           <t>uds</t>
         </is>
       </c>
-      <c r="D37" s="13" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+      <c r="D37" s="13" t="n">
+        <v>40</v>
       </c>
       <c r="E37" s="14">
         <f>IF(B37="","",IF(B37&lt;D37,"⚠️ PEDIR","OK"))</f>
@@ -1633,10 +1592,8 @@
           <t>uds</t>
         </is>
       </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+      <c r="D38" s="9" t="n">
+        <v>40</v>
       </c>
       <c r="E38" s="10">
         <f>IF(B38="","",IF(B38&lt;D38,"⚠️ PEDIR","OK"))</f>
@@ -1663,10 +1620,8 @@
           <t>sets</t>
         </is>
       </c>
-      <c r="D40" s="9" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+      <c r="D40" s="9" t="n">
+        <v>60</v>
       </c>
       <c r="E40" s="10">
         <f>IF(B40="","",IF(B40&lt;D40,"⚠️ PEDIR","OK"))</f>
@@ -1686,10 +1641,8 @@
           <t>uds</t>
         </is>
       </c>
-      <c r="D41" s="13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+      <c r="D41" s="13" t="n">
+        <v>100</v>
       </c>
       <c r="E41" s="14">
         <f>IF(B41="","",IF(B41&lt;D41,"⚠️ PEDIR","OK"))</f>
@@ -1709,10 +1662,8 @@
           <t>uds</t>
         </is>
       </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+      <c r="D42" s="9" t="n">
+        <v>60</v>
       </c>
       <c r="E42" s="10">
         <f>IF(B42="","",IF(B42&lt;D42,"⚠️ PEDIR","OK"))</f>
@@ -1732,10 +1683,8 @@
           <t>uds</t>
         </is>
       </c>
-      <c r="D43" s="13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="D43" s="13" t="n">
+        <v>20</v>
       </c>
       <c r="E43" s="14">
         <f>IF(B43="","",IF(B43&lt;D43,"⚠️ PEDIR","OK"))</f>
@@ -1743,6 +1692,7 @@
       </c>
       <c r="F43" s="12" t="n"/>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="15" t="inlineStr">
         <is>
@@ -1753,14 +1703,14 @@
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A34:F34"/>
     <mergeCell ref="A39:F39"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A45:F45"/>
-    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -2170,7 +2120,7 @@
       </c>
       <c r="D22" s="19">
         <f>COUNTIFS(B5:B20,"?*",F5:F20,"✓")</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="E22" s="18" t="inlineStr">
         <is>
@@ -2179,7 +2129,7 @@
       </c>
       <c r="F22">
         <f>COUNTIF(B5:B20,"?*")-COUNTIF(F5:F20,"N/A")</f>
-        <v>9.0</v>
+        <v/>
       </c>
     </row>
     <row r="23"/>
@@ -2201,13 +2151,13 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="7">
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A24:G24"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A24:G24"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A26:G26"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:G20">
     <cfRule type="expression" priority="1" dxfId="0">
@@ -2599,7 +2549,7 @@
       </c>
       <c r="D21" s="19">
         <f>COUNTIFS(B5:B19,"?*",F5:F19,"✓")</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="E21" s="18" t="inlineStr">
         <is>
@@ -2608,7 +2558,7 @@
       </c>
       <c r="F21">
         <f>COUNTIF(B5:B19,"?*")-COUNTIF(F5:F19,"N/A")</f>
-        <v>8.0</v>
+        <v/>
       </c>
     </row>
     <row r="22"/>
@@ -2665,9 +2615,9 @@
           <t>Congélalos el día que llegan, no el día que caducan en fresco</t>
         </is>
       </c>
-      <c r="E27" s="35" t="n"/>
-      <c r="F27" s="35" t="n"/>
-      <c r="G27" s="36" t="n"/>
+      <c r="E27" s="37" t="n"/>
+      <c r="F27" s="37" t="n"/>
+      <c r="G27" s="38" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="20" t="n"/>
@@ -2686,9 +2636,9 @@
           <t>Toda la superficie está expuesta: se enrancia mucho antes que una pieza entera</t>
         </is>
       </c>
-      <c r="E28" s="35" t="n"/>
-      <c r="F28" s="35" t="n"/>
-      <c r="G28" s="36" t="n"/>
+      <c r="E28" s="37" t="n"/>
+      <c r="F28" s="37" t="n"/>
+      <c r="G28" s="38" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="20" t="n"/>
@@ -2707,9 +2657,9 @@
           <t>La grasa se enrancia aunque esté congelado; si es para servir crudo, la congelación cuenta además como tratamiento anti-ANISAKIS</t>
         </is>
       </c>
-      <c r="E29" s="35" t="n"/>
-      <c r="F29" s="35" t="n"/>
-      <c r="G29" s="36" t="n"/>
+      <c r="E29" s="37" t="n"/>
+      <c r="F29" s="37" t="n"/>
+      <c r="G29" s="38" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="20" t="n"/>
@@ -2728,9 +2678,9 @@
           <t>Congélalo en porciones planas: se descongela antes y con menos pérdida</t>
         </is>
       </c>
-      <c r="E30" s="35" t="n"/>
-      <c r="F30" s="35" t="n"/>
-      <c r="G30" s="36" t="n"/>
+      <c r="E30" s="37" t="n"/>
+      <c r="F30" s="37" t="n"/>
+      <c r="G30" s="38" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="20" t="n"/>
@@ -2749,9 +2699,9 @@
           <t>Etiquetar con fecha de producción Y de congelación: la vida útil de esta tabla se cuenta desde la de congelación</t>
         </is>
       </c>
-      <c r="E31" s="35" t="n"/>
-      <c r="F31" s="35" t="n"/>
-      <c r="G31" s="36" t="n"/>
+      <c r="E31" s="37" t="n"/>
+      <c r="F31" s="37" t="n"/>
+      <c r="G31" s="38" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="20" t="n"/>
@@ -2770,9 +2720,9 @@
           <t>Congelar el mismo día en porciones planas y regenerar por encima de 75 °C: el arroz cocido templado es el clásico de la toxiinfección</t>
         </is>
       </c>
-      <c r="E32" s="35" t="n"/>
-      <c r="F32" s="35" t="n"/>
-      <c r="G32" s="36" t="n"/>
+      <c r="E32" s="37" t="n"/>
+      <c r="F32" s="37" t="n"/>
+      <c r="G32" s="38" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="20" t="n"/>
@@ -2791,9 +2741,9 @@
           <t>Pierde textura antes que seguridad; descongela y regenera en horno</t>
         </is>
       </c>
-      <c r="E33" s="35" t="n"/>
-      <c r="F33" s="35" t="n"/>
-      <c r="G33" s="36" t="n"/>
+      <c r="E33" s="37" t="n"/>
+      <c r="F33" s="37" t="n"/>
+      <c r="G33" s="38" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="20" t="n"/>
@@ -2812,9 +2762,9 @@
           <t>Se deshacen al descongelar: en un bowl se ven, así que se piden frescos y se rota con FIFO</t>
         </is>
       </c>
-      <c r="E34" s="35" t="n"/>
-      <c r="F34" s="35" t="n"/>
-      <c r="G34" s="36" t="n"/>
+      <c r="E34" s="37" t="n"/>
+      <c r="F34" s="37" t="n"/>
+      <c r="G34" s="38" t="n"/>
     </row>
     <row r="35"/>
     <row r="36">
@@ -2827,23 +2777,23 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="17">
-    <mergeCell ref="D28:G28"/>
     <mergeCell ref="A36:G36"/>
     <mergeCell ref="D31:G31"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="D26:G26"/>
+    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="D30:G30"/>
+    <mergeCell ref="A2:G2"/>
     <mergeCell ref="D33:G33"/>
+    <mergeCell ref="D34:G34"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="D27:G27"/>
+    <mergeCell ref="A21:C21"/>
     <mergeCell ref="D32:G32"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="D29:G29"/>
-    <mergeCell ref="D27:G27"/>
-    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="D28:G28"/>
+    <mergeCell ref="A5:G5"/>
     <mergeCell ref="A23:G23"/>
-    <mergeCell ref="D30:G30"/>
-    <mergeCell ref="D34:G34"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A11:G11"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:G19">
     <cfRule type="expression" priority="1" dxfId="0">
@@ -3329,7 +3279,7 @@
       </c>
       <c r="D25" s="19">
         <f>COUNTIFS(B5:B23,"?*",F5:F23,"✓")</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="E25" s="18" t="inlineStr">
         <is>
@@ -3338,7 +3288,7 @@
       </c>
       <c r="F25">
         <f>COUNTIF(B5:B23,"?*")-COUNTIF(F5:F23,"N/A")</f>
-        <v>11.0</v>
+        <v/>
       </c>
     </row>
     <row r="26"/>
@@ -3360,14 +3310,14 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="8">
+    <mergeCell ref="A25:C25"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A27:G27"/>
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A29:G29"/>
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A29:G29"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:G23">
     <cfRule type="expression" priority="1" dxfId="0">
@@ -3809,7 +3759,7 @@
       </c>
       <c r="D25" s="19">
         <f>COUNTIFS(B5:B23,"?*",F5:F23,"✓")</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="E25" s="18" t="inlineStr">
         <is>
@@ -3818,7 +3768,7 @@
       </c>
       <c r="F25">
         <f>COUNTIF(B5:B23,"?*")-COUNTIF(F5:F23,"N/A")</f>
-        <v>11.0</v>
+        <v/>
       </c>
     </row>
     <row r="26"/>
@@ -3840,14 +3790,14 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="8">
+    <mergeCell ref="A25:C25"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A27:G27"/>
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A11:G11"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A29:G29"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:G23">
     <cfRule type="expression" priority="1" dxfId="0">

--- a/astro-site/public/dl/kit-tareas-dark-kitchen/05-tareas-semanales-mensuales.xlsx
+++ b/astro-site/public/dl/kit-tareas-dark-kitchen/05-tareas-semanales-mensuales.xlsx
@@ -2120,7 +2120,7 @@
       </c>
       <c r="D22" s="19">
         <f>COUNTIFS(B5:B20,"?*",F5:F20,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E22" s="18" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="F22">
         <f>COUNTIF(B5:B20,"?*")-COUNTIF(F5:F20,"N/A")</f>
-        <v/>
+        <v>9.0</v>
       </c>
     </row>
     <row r="23"/>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="D21" s="19">
         <f>COUNTIFS(B5:B19,"?*",F5:F19,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E21" s="18" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="F21">
         <f>COUNTIF(B5:B19,"?*")-COUNTIF(F5:F19,"N/A")</f>
-        <v/>
+        <v>8.0</v>
       </c>
     </row>
     <row r="22"/>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="D25" s="19">
         <f>COUNTIFS(B5:B23,"?*",F5:F23,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E25" s="18" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="F25">
         <f>COUNTIF(B5:B23,"?*")-COUNTIF(F5:F23,"N/A")</f>
-        <v/>
+        <v>11.0</v>
       </c>
     </row>
     <row r="26"/>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="D25" s="19">
         <f>COUNTIFS(B5:B23,"?*",F5:F23,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E25" s="18" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="F25">
         <f>COUNTIF(B5:B23,"?*")-COUNTIF(F5:F23,"N/A")</f>
-        <v/>
+        <v>11.0</v>
       </c>
     </row>
     <row r="26"/>
